--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levels" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="percent change" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="charts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,6 +774,1077 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  No imports  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$J$2:$J$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="71.50952316672017"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  GSOO exp  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$K$2:$K$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="7.709110301617583"/>
+          <min val="-0.7561469943685784"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  Res20%  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$L$2:$L$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="22.5482665569533"/>
+          <min val="-0.766637447044205"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  DC series NSW  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$M$2:$M$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="2.916091695439627"/>
+          <min val="-1.598763468300524"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-H L-M  ·  DC series NSW  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$N$2:$N$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="9.792466076806662"/>
+          <min val="-2.485651486958362"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  DC series NSW  ·  No imports  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!O1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$O$2:$O$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="84.8294911052738"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!P1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$P$2:$P$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="6.804428502432081"/>
+          <min val="-20.55297289021944"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!Q1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$Q$2:$Q$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="10.49938730093463"/>
+          <min val="-17.75961406819361"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!R1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$R$2:$R$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="21.04672645786252"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
@@ -1415,6 +2487,839 @@
     <legend>
       <legendPos val="r"/>
     </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Acc  ·  W-M L-M  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$C$2:$C$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0"/>
+          <min val="-23.41393780692444"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SG  ·  W-M L-M  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$D$2:$D$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="54.59209976168378"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-L  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$E$2:$E$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0"/>
+          <min val="-28.06269185567489"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-H  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$F$2:$F$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="55.36705390895715"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-L L-M  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$G$2:$G$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="18.31120174232388"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-H L-M  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$H$2:$H$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5.675792059208939"/>
+          <min val="-2.758179777732517"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SC  ·  W-M L-M  ·  Dunk27  ·  Netback</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'percent change'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'percent change'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'percent change'!$I$2:$I$27</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.4077645643328687"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% vs central</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1467,6 +3372,363 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="10" name="Chart 10"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="11" name="Chart 11"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="12" name="Chart 12"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="13" name="Chart 13"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="14" name="Chart 14"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="15" name="Chart 15"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="16" name="Chart 16"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4882,4 +7144,18 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -3446,6 +3446,8 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="22.0"/>
+          <c:min val="8.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -3467,7 +3469,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -3746,7 +3748,7 @@
         <c:axId val="50100002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="71.50952316672017"/>
+          <c:max val="72.0"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -3769,7 +3771,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50100001"/>
         <c:crosses val="autoZero"/>
@@ -4044,8 +4046,8 @@
         <c:axId val="50110002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="7.709110301617583"/>
-          <c:min val="-0.7561469943685784"/>
+          <c:max val="8.0"/>
+          <c:min val="-1.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -4067,7 +4069,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50110001"/>
         <c:crosses val="autoZero"/>
@@ -4342,8 +4344,8 @@
         <c:axId val="50120002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="22.5482665569533"/>
-          <c:min val="-0.766637447044205"/>
+          <c:max val="23.0"/>
+          <c:min val="-1.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -4365,7 +4367,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50120001"/>
         <c:crosses val="autoZero"/>
@@ -4640,8 +4642,8 @@
         <c:axId val="50130002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2.9160916954396265"/>
-          <c:min val="-1.5987634683005236"/>
+          <c:max val="3.0"/>
+          <c:min val="-2.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -4663,7 +4665,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50130001"/>
         <c:crosses val="autoZero"/>
@@ -4938,8 +4940,8 @@
         <c:axId val="50140002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="9.792466076806662"/>
-          <c:min val="-2.4856514869583624"/>
+          <c:max val="10.0"/>
+          <c:min val="-2.5"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -4961,7 +4963,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50140001"/>
         <c:crosses val="autoZero"/>
@@ -5236,7 +5238,7 @@
         <c:axId val="50150002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="84.8294911052738"/>
+          <c:max val="85.0"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -5259,7 +5261,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50150001"/>
         <c:crosses val="autoZero"/>
@@ -5534,8 +5536,8 @@
         <c:axId val="50160002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6.8044285024320805"/>
-          <c:min val="-20.552972890219444"/>
+          <c:max val="7.0"/>
+          <c:min val="-21.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -5557,7 +5559,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50160001"/>
         <c:crosses val="autoZero"/>
@@ -5832,8 +5834,8 @@
         <c:axId val="50170002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10.499387300934625"/>
-          <c:min val="-17.759614068193606"/>
+          <c:max val="10.5"/>
+          <c:min val="-18.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -5855,7 +5857,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50170001"/>
         <c:crosses val="autoZero"/>
@@ -6130,7 +6132,7 @@
         <c:axId val="50180002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="21.04672645786252"/>
+          <c:max val="21.5"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -6153,7 +6155,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50180001"/>
         <c:crosses val="autoZero"/>
@@ -9500,6 +9502,8 @@
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="85.0"/>
+          <c:min val="-28.5"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -9521,7 +9525,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -9801,7 +9805,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.0"/>
-          <c:min val="-23.413937806924444"/>
+          <c:min val="-23.5"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -9823,7 +9827,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -10098,7 +10102,7 @@
         <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="54.59209976168378"/>
+          <c:max val="55.0"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -10121,7 +10125,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -10397,7 +10401,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.0"/>
-          <c:min val="-28.062691855674892"/>
+          <c:min val="-28.5"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -10419,7 +10423,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50050001"/>
         <c:crosses val="autoZero"/>
@@ -10694,7 +10698,7 @@
         <c:axId val="50060002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="55.36705390895715"/>
+          <c:max val="55.5"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -10717,7 +10721,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50060001"/>
         <c:crosses val="autoZero"/>
@@ -10992,7 +10996,7 @@
         <c:axId val="50070002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="18.31120174232388"/>
+          <c:max val="18.5"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -11015,7 +11019,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50070001"/>
         <c:crosses val="autoZero"/>
@@ -11290,8 +11294,8 @@
         <c:axId val="50080002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="5.6757920592089395"/>
-          <c:min val="-2.7581797777325168"/>
+          <c:max val="6.0"/>
+          <c:min val="-3.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -11313,7 +11317,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50080001"/>
         <c:crosses val="autoZero"/>
@@ -11588,7 +11592,7 @@
         <c:axId val="50090002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="0.4077645643328687"/>
+          <c:max val="0.5"/>
           <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -11611,7 +11615,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50090001"/>
         <c:crosses val="autoZero"/>

--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -48,7 +48,7 @@
     <t>SC  ·  W-M L-M  ·  GSOO exp  ·  Netback</t>
   </si>
   <si>
-    <t>SC  ·  W-M L-M  ·  Res20%  ·  Netback</t>
+    <t>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</t>
   </si>
   <si>
     <t>SC  ·  W-M L-M  ·  DC series NSW  ·  Netback</t>
@@ -60,13 +60,13 @@
     <t>SC  ·  W-M L-M  ·  DC series NSW  ·  No imports  ·  Netback</t>
   </si>
   <si>
-    <t>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</t>
+    <t>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</t>
   </si>
   <si>
-    <t>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</t>
+    <t>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</t>
   </si>
   <si>
-    <t>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</t>
+    <t>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</t>
   </si>
   <si>
     <t>Year</t>
@@ -2071,7 +2071,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2839,7 +2839,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3031,7 +3031,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3223,7 +3223,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4101,7 +4101,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SC  ·  W-M L-M  ·  Res20%  ·  Netback</a:t>
+              <a:t>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4121,7 +4121,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5293,7 +5293,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</a:t>
+              <a:t>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5313,7 +5313,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5591,7 +5591,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</a:t>
+              <a:t>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5611,7 +5611,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5889,7 +5889,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</a:t>
+              <a:t>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5909,7 +5909,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8127,7 +8127,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8895,7 +8895,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9087,7 +9087,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%+contract  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9279,7 +9279,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SC  ·  W-M L-M  ·  Res20%  ·  DC series NSW  ·  Netback</c:v>
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>

--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -2173,37 +2173,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>10.79559326171875</c:v>
+                  <c:v>10.80988597869873</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.07336711883545</c:v>
+                  <c:v>11.08655166625977</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.32161712646484</c:v>
+                  <c:v>11.33691310882568</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.56055068969727</c:v>
+                  <c:v>11.57836532592773</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.59040069580078</c:v>
+                  <c:v>12.3137035369873</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.25686073303223</c:v>
+                  <c:v>12.26032733917236</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.40457725524902</c:v>
+                  <c:v>12.41421699523926</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.59483242034912</c:v>
+                  <c:v>12.60287666320801</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.8024959564209</c:v>
+                  <c:v>12.79858112335205</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.11048316955566</c:v>
+                  <c:v>13.01634979248047</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.47591114044189</c:v>
+                  <c:v>13.4949893951416</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>10.9560375213623</c:v>
@@ -3133,43 +3133,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>9.347173690795898</c:v>
+                  <c:v>9.395079612731934</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.621140480041504</c:v>
+                  <c:v>9.646550178527832</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.303424835205078</c:v>
+                  <c:v>9.358547210693359</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.01430702209473</c:v>
+                  <c:v>10.06110095977783</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.54446506500244</c:v>
+                  <c:v>10.59013175964355</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.67580986022949</c:v>
+                  <c:v>10.72100162506104</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.95539379119873</c:v>
+                  <c:v>11.01472091674805</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.11550998687744</c:v>
+                  <c:v>11.17118263244629</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.49686908721924</c:v>
+                  <c:v>11.55814170837402</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.66549205780029</c:v>
+                  <c:v>11.71694374084473</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.04719829559326</c:v>
+                  <c:v>12.06698322296143</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.13586902618408</c:v>
+                  <c:v>11.14333057403564</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.08155918121338</c:v>
+                  <c:v>11.08236408233643</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>10.93555450439453</c:v>
@@ -4223,37 +4223,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.06955364382239537</c:v>
+                  <c:v>0.2020397216015546</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.2168264025826372</c:v>
+                  <c:v>-0.09801918068477189</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.08079587307090463</c:v>
+                  <c:v>0.216009250385607</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.68536724490822</c:v>
+                  <c:v>1.84206287957589</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.323255496719945</c:v>
+                  <c:v>0.07451419288433403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9425916278498425</c:v>
+                  <c:v>0.97114120637245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.766637447044205</c:v>
+                  <c:v>-0.6895220570003913</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.766866380129154</c:v>
+                  <c:v>5.834419034359839</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.104423391107595</c:v>
+                  <c:v>8.071366495559996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.84432725549598</c:v>
+                  <c:v>10.04846407339621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>22.5482665569533</c:v>
+                  <c:v>14.24410812793835</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7.649768807982493</c:v>
@@ -4344,7 +4344,7 @@
         <c:axId val="50120002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="23.0"/>
+          <c:max val="14.5"/>
           <c:min val="-1.0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -5713,43 +5713,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>-13.35654499081164</c:v>
+                  <c:v>-12.91248192648389</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-13.30297998590297</c:v>
+                  <c:v>-13.07401075478206</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-17.75961406819361</c:v>
+                  <c:v>-17.27234346474016</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.91522665503473</c:v>
+                  <c:v>-11.50363218467939</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.30423709371396</c:v>
+                  <c:v>-13.93309998883915</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-12.07830956963808</c:v>
+                  <c:v>-11.70612831036683</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-12.35972483202532</c:v>
+                  <c:v>-11.88512339759361</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.655950607997918</c:v>
+                  <c:v>-6.188431782150339</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-2.920304938386131</c:v>
+                  <c:v>-2.402918219253625</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.372542679902722</c:v>
+                  <c:v>-0.9375375683850384</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.987588461237877</c:v>
+                  <c:v>2.155081099829026</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.416723318745124</c:v>
+                  <c:v>9.490037589493493</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.49938730093463</c:v>
+                  <c:v>10.50741334487664</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8.579472946271505</c:v>
@@ -5834,8 +5834,8 @@
         <c:axId val="50170002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10.5"/>
-          <c:min val="-18.0"/>
+          <c:max val="11.0"/>
+          <c:min val="-17.5"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -8229,37 +8229,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.06955364382239537</c:v>
+                  <c:v>0.2020397216015546</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.2168264025826372</c:v>
+                  <c:v>-0.09801918068477189</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.08079587307090463</c:v>
+                  <c:v>0.216009250385607</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.68536724490822</c:v>
+                  <c:v>1.84206287957589</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.323255496719945</c:v>
+                  <c:v>0.07451419288433403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9425916278498425</c:v>
+                  <c:v>0.97114120637245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.766637447044205</c:v>
+                  <c:v>-0.6895220570003913</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.766866380129154</c:v>
+                  <c:v>5.834419034359839</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.104423391107595</c:v>
+                  <c:v>8.071366495559996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.84432725549598</c:v>
+                  <c:v>10.04846407339621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>22.5482665569533</c:v>
+                  <c:v>14.24410812793835</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7.649768807982493</c:v>
@@ -9189,43 +9189,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>-13.35654499081164</c:v>
+                  <c:v>-12.91248192648389</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-13.30297998590297</c:v>
+                  <c:v>-13.07401075478206</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-17.75961406819361</c:v>
+                  <c:v>-17.27234346474016</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.91522665503473</c:v>
+                  <c:v>-11.50363218467939</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.30423709371396</c:v>
+                  <c:v>-13.93309998883915</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-12.07830956963808</c:v>
+                  <c:v>-11.70612831036683</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-12.35972483202532</c:v>
+                  <c:v>-11.88512339759361</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.655950607997918</c:v>
+                  <c:v>-6.188431782150339</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-2.920304938386131</c:v>
+                  <c:v>-2.402918219253625</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.372542679902722</c:v>
+                  <c:v>-0.9375375683850384</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.987588461237877</c:v>
+                  <c:v>2.155081099829026</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.416723318745124</c:v>
+                  <c:v>9.490037589493493</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.49938730093463</c:v>
+                  <c:v>10.50741334487664</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8.579472946271505</c:v>
@@ -12566,7 +12566,7 @@
         <v>10.78849792480469</v>
       </c>
       <c r="L2">
-        <v>10.79559326171875</v>
+        <v>10.80988597869873</v>
       </c>
       <c r="M2">
         <v>10.82431983947754</v>
@@ -12581,7 +12581,7 @@
         <v>9.072551727294922</v>
       </c>
       <c r="Q2">
-        <v>9.347173690795898</v>
+        <v>9.395079612731934</v>
       </c>
       <c r="R2">
         <v>10.90130519866943</v>
@@ -12622,7 +12622,7 @@
         <v>11.09786701202393</v>
       </c>
       <c r="L3">
-        <v>11.07336711883545</v>
+        <v>11.08655166625977</v>
       </c>
       <c r="M3">
         <v>11.10275936126709</v>
@@ -12637,7 +12637,7 @@
         <v>9.449390411376953</v>
       </c>
       <c r="Q3">
-        <v>9.621140480041504</v>
+        <v>9.646550178527832</v>
       </c>
       <c r="R3">
         <v>11.18279361724854</v>
@@ -12678,7 +12678,7 @@
         <v>11.31296348571777</v>
       </c>
       <c r="L4">
-        <v>11.32161712646484</v>
+        <v>11.33691310882568</v>
       </c>
       <c r="M4">
         <v>11.32342147827148</v>
@@ -12693,7 +12693,7 @@
         <v>8.9874267578125</v>
       </c>
       <c r="Q4">
-        <v>9.303424835205078</v>
+        <v>9.358547210693359</v>
       </c>
       <c r="R4">
         <v>11.44109439849854</v>
@@ -12734,7 +12734,7 @@
         <v>11.36948013305664</v>
       </c>
       <c r="L5">
-        <v>11.56055068969727</v>
+        <v>11.57836532592773</v>
       </c>
       <c r="M5">
         <v>11.44236660003662</v>
@@ -12749,7 +12749,7 @@
         <v>9.667744636535645</v>
       </c>
       <c r="Q5">
-        <v>10.01430702209473</v>
+        <v>10.06110095977783</v>
       </c>
       <c r="R5">
         <v>11.73096370697021</v>
@@ -12790,7 +12790,7 @@
         <v>12.26796245574951</v>
       </c>
       <c r="L6">
-        <v>12.59040069580078</v>
+        <v>12.3137035369873</v>
       </c>
       <c r="M6">
         <v>12.4367504119873</v>
@@ -12805,7 +12805,7 @@
         <v>10.21038818359375</v>
       </c>
       <c r="Q6">
-        <v>10.54446506500244</v>
+        <v>10.59013175964355</v>
       </c>
       <c r="R6">
         <v>12.40548324584961</v>
@@ -12846,7 +12846,7 @@
         <v>12.05098724365234</v>
       </c>
       <c r="L7">
-        <v>12.25686073303223</v>
+        <v>12.26032733917236</v>
       </c>
       <c r="M7">
         <v>12.07330703735352</v>
@@ -12861,7 +12861,7 @@
         <v>10.09014797210693</v>
       </c>
       <c r="Q7">
-        <v>10.67580986022949</v>
+        <v>10.72100162506104</v>
       </c>
       <c r="R7">
         <v>12.3315315246582</v>
@@ -12902,7 +12902,7 @@
         <v>12.41473579406738</v>
       </c>
       <c r="L8">
-        <v>12.40457725524902</v>
+        <v>12.41421699523926</v>
       </c>
       <c r="M8">
         <v>12.30055809020996</v>
@@ -12917,7 +12917,7 @@
         <v>10.26397705078125</v>
       </c>
       <c r="Q8">
-        <v>10.95539379119873</v>
+        <v>11.01472091674805</v>
       </c>
       <c r="R8">
         <v>12.50614356994629</v>
@@ -12958,7 +12958,7 @@
         <v>11.824538230896</v>
       </c>
       <c r="L9">
-        <v>12.59483242034912</v>
+        <v>12.60287666320801</v>
       </c>
       <c r="M9">
         <v>11.93213081359863</v>
@@ -12973,7 +12973,7 @@
         <v>10.6655445098877</v>
       </c>
       <c r="Q9">
-        <v>11.11550998687744</v>
+        <v>11.17118263244629</v>
       </c>
       <c r="R9">
         <v>12.71953868865967</v>
@@ -13014,7 +13014,7 @@
         <v>11.75459957122803</v>
       </c>
       <c r="L10">
-        <v>12.8024959564209</v>
+        <v>12.79858112335205</v>
       </c>
       <c r="M10">
         <v>11.88990116119385</v>
@@ -13029,7 +13029,7 @@
         <v>10.86591625213623</v>
       </c>
       <c r="Q10">
-        <v>11.49686908721924</v>
+        <v>11.55814170837402</v>
       </c>
       <c r="R10">
         <v>12.9487190246582</v>
@@ -13070,7 +13070,7 @@
         <v>11.74276924133301</v>
       </c>
       <c r="L11">
-        <v>13.11048316955566</v>
+        <v>13.01634979248047</v>
       </c>
       <c r="M11">
         <v>11.92905712127686</v>
@@ -13085,7 +13085,7 @@
         <v>11.22132968902588</v>
       </c>
       <c r="Q11">
-        <v>11.66549205780029</v>
+        <v>11.71694374084473</v>
       </c>
       <c r="R11">
         <v>13.24100017547607</v>
@@ -13126,7 +13126,7 @@
         <v>11.72309684753418</v>
       </c>
       <c r="L12">
-        <v>14.47591114044189</v>
+        <v>13.4949893951416</v>
       </c>
       <c r="M12">
         <v>12.01075172424316</v>
@@ -13141,7 +13141,7 @@
         <v>11.824462890625</v>
       </c>
       <c r="Q12">
-        <v>12.04719829559326</v>
+        <v>12.06698322296143</v>
       </c>
       <c r="R12">
         <v>14.29854297637939</v>
@@ -13197,7 +13197,7 @@
         <v>10.64111328125</v>
       </c>
       <c r="Q13">
-        <v>11.13586902618408</v>
+        <v>11.14333057403564</v>
       </c>
       <c r="R13">
         <v>11.22103595733643</v>
@@ -13253,7 +13253,7 @@
         <v>10.5792407989502</v>
       </c>
       <c r="Q14">
-        <v>11.08155918121338</v>
+        <v>11.08236408233643</v>
       </c>
       <c r="R14">
         <v>11.09693908691406</v>
@@ -14089,7 +14089,7 @@
         <v>0.003783548494662448</v>
       </c>
       <c r="L2">
-        <v>0.06955364382239537</v>
+        <v>0.2020397216015546</v>
       </c>
       <c r="M2">
         <v>0.3358341292339917</v>
@@ -14104,7 +14104,7 @@
         <v>-15.90214824225884</v>
       </c>
       <c r="Q2">
-        <v>-13.35654499081164</v>
+        <v>-12.91248192648389</v>
       </c>
       <c r="R2">
         <v>1.049448503606576</v>
@@ -14145,7 +14145,7 @@
         <v>0.003944485703510914</v>
       </c>
       <c r="L3">
-        <v>-0.2168264025826372</v>
+        <v>-0.09801918068477189</v>
       </c>
       <c r="M3">
         <v>0.04802991415457925</v>
@@ -14160,7 +14160,7 @@
         <v>-14.85063633405858</v>
       </c>
       <c r="Q3">
-        <v>-13.30297998590297</v>
+        <v>-13.07401075478206</v>
       </c>
       <c r="R3">
         <v>0.7692262740903733</v>
@@ -14201,7 +14201,7 @@
         <v>0.004299446501065951</v>
       </c>
       <c r="L4">
-        <v>0.08079587307090463</v>
+        <v>0.216009250385607</v>
       </c>
       <c r="M4">
         <v>0.09674597656110784</v>
@@ -14216,7 +14216,7 @@
         <v>-20.55297289021944</v>
       </c>
       <c r="Q4">
-        <v>-17.75961406819361</v>
+        <v>-17.27234346474016</v>
       </c>
       <c r="R4">
         <v>1.136950690912619</v>
@@ -14257,7 +14257,7 @@
         <v>0.00473106734222295</v>
       </c>
       <c r="L5">
-        <v>1.68536724490822</v>
+        <v>1.84206287957589</v>
       </c>
       <c r="M5">
         <v>0.6458326342985599</v>
@@ -14272,7 +14272,7 @@
         <v>-14.96355232694695</v>
       </c>
       <c r="Q5">
-        <v>-11.91522665503473</v>
+        <v>-11.50363218467939</v>
       </c>
       <c r="R5">
         <v>3.1843019159145</v>
@@ -14313,7 +14313,7 @@
         <v>-0.2972274581778067</v>
       </c>
       <c r="L6">
-        <v>2.323255496719945</v>
+        <v>0.07451419288433403</v>
       </c>
       <c r="M6">
         <v>1.074526593831759</v>
@@ -14328,7 +14328,7 @@
         <v>-17.01930827515222</v>
       </c>
       <c r="Q6">
-        <v>-14.30423709371396</v>
+        <v>-13.93309998883915</v>
       </c>
       <c r="R6">
         <v>0.8204156797579243</v>
@@ -14369,7 +14369,7 @@
         <v>-0.75289990282148</v>
       </c>
       <c r="L7">
-        <v>0.9425916278498425</v>
+        <v>0.97114120637245</v>
       </c>
       <c r="M7">
         <v>-0.5690830291644744</v>
@@ -14384,7 +14384,7 @@
         <v>-16.90158610776724</v>
       </c>
       <c r="Q7">
-        <v>-12.07830956963808</v>
+        <v>-11.70612831036683</v>
       </c>
       <c r="R7">
         <v>1.557550334634827</v>
@@ -14425,7 +14425,7 @@
         <v>-0.6853718025302769</v>
       </c>
       <c r="L8">
-        <v>-0.766637447044205</v>
+        <v>-0.6895220570003913</v>
       </c>
       <c r="M8">
         <v>-1.598763468300524</v>
@@ -14440,7 +14440,7 @@
         <v>-17.89087729818434</v>
       </c>
       <c r="Q8">
-        <v>-12.35972483202532</v>
+        <v>-11.88512339759361</v>
       </c>
       <c r="R8">
         <v>0.04586641521007184</v>
@@ -14481,7 +14481,7 @@
         <v>-0.7017867857237792</v>
       </c>
       <c r="L9">
-        <v>5.766866380129154</v>
+        <v>5.834419034359839</v>
       </c>
       <c r="M9">
         <v>0.201736972148292</v>
@@ -14496,7 +14496,7 @@
         <v>-10.43459861950725</v>
       </c>
       <c r="Q9">
-        <v>-6.655950607997918</v>
+        <v>-6.188431782150339</v>
       </c>
       <c r="R9">
         <v>6.814104705893276</v>
@@ -14537,7 +14537,7 @@
         <v>-0.7440257613474111</v>
       </c>
       <c r="L10">
-        <v>8.104423391107595</v>
+        <v>8.071366495559996</v>
       </c>
       <c r="M10">
         <v>0.3984624235302547</v>
@@ -14552,7 +14552,7 @@
         <v>-8.248077948884458</v>
       </c>
       <c r="Q10">
-        <v>-2.920304938386131</v>
+        <v>-2.402918219253625</v>
       </c>
       <c r="R10">
         <v>9.339132664368055</v>
@@ -14593,7 +14593,7 @@
         <v>-0.7191924326155674</v>
       </c>
       <c r="L11">
-        <v>10.84432725549598</v>
+        <v>10.04846407339621</v>
       </c>
       <c r="M11">
         <v>0.8558032758704481</v>
@@ -14608,7 +14608,7 @@
         <v>-5.127772622406512</v>
       </c>
       <c r="Q11">
-        <v>-1.372542679902722</v>
+        <v>-0.9375375683850384</v>
       </c>
       <c r="R11">
         <v>11.94780067669254</v>
@@ -14649,7 +14649,7 @@
         <v>-0.7561469943685784</v>
       </c>
       <c r="L12">
-        <v>22.5482665569533</v>
+        <v>14.24410812793835</v>
       </c>
       <c r="M12">
         <v>1.679043866181562</v>
@@ -14664,7 +14664,7 @@
         <v>0.1019843348444738</v>
       </c>
       <c r="Q12">
-        <v>1.987588461237877</v>
+        <v>2.155081099829026</v>
       </c>
       <c r="R12">
         <v>21.04672645786252</v>
@@ -14720,7 +14720,7 @@
         <v>4.555445557079296</v>
       </c>
       <c r="Q13">
-        <v>9.416723318745124</v>
+        <v>9.490037589493493</v>
       </c>
       <c r="R13">
         <v>10.25354050112142</v>
@@ -14776,7 +14776,7 @@
         <v>5.490536780677702</v>
       </c>
       <c r="Q14">
-        <v>10.49938730093463</v>
+        <v>10.50741334487664</v>
       </c>
       <c r="R14">
         <v>10.65274750313005</v>

--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -2173,37 +2173,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>10.80988597869873</c:v>
+                  <c:v>10.89763832092285</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.08655166625977</c:v>
+                  <c:v>11.17911243438721</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.33691310882568</c:v>
+                  <c:v>11.4369945526123</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.57836532592773</c:v>
+                  <c:v>11.68558597564697</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.3137035369873</c:v>
+                  <c:v>12.70683670043945</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.26032733917236</c:v>
+                  <c:v>12.33250141143799</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.41421699523926</c:v>
+                  <c:v>12.50737571716309</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.60287666320801</c:v>
+                  <c:v>12.69899463653564</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.79858112335205</c:v>
+                  <c:v>12.8897762298584</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.01634979248047</c:v>
+                  <c:v>13.10569000244141</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.4949893951416</c:v>
+                  <c:v>13.70723533630371</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>10.9560375213623</c:v>
@@ -4223,37 +4223,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.2020397216015546</c:v>
+                  <c:v>1.015458447620654</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.09801918068477189</c:v>
+                  <c:v>0.7360547821174457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.216009250385607</c:v>
+                  <c:v>1.100708885994872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.84206287957589</c:v>
+                  <c:v>2.785164245210203</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.07451419288433403</c:v>
+                  <c:v>3.26954079291657</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.97114120637245</c:v>
+                  <c:v>1.565537933357675</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.6895220570003913</c:v>
+                  <c:v>0.05572326957656859</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.834419034359839</c:v>
+                  <c:v>6.641583155515418</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.071366495559996</c:v>
+                  <c:v>8.841419025825781</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.04846407339621</c:v>
+                  <c:v>10.80380278531956</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.24410812793835</c:v>
+                  <c:v>16.040911929842</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7.649768807982493</c:v>
@@ -4344,8 +4344,8 @@
         <c:axId val="50120002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="14.5"/>
-          <c:min val="-1.0"/>
+          <c:max val="16.5"/>
+          <c:min val="0.0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
@@ -8229,37 +8229,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.2020397216015546</c:v>
+                  <c:v>1.015458447620654</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.09801918068477189</c:v>
+                  <c:v>0.7360547821174457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.216009250385607</c:v>
+                  <c:v>1.100708885994872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.84206287957589</c:v>
+                  <c:v>2.785164245210203</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.07451419288433403</c:v>
+                  <c:v>3.26954079291657</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.97114120637245</c:v>
+                  <c:v>1.565537933357675</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.6895220570003913</c:v>
+                  <c:v>0.05572326957656859</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.834419034359839</c:v>
+                  <c:v>6.641583155515418</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.071366495559996</c:v>
+                  <c:v>8.841419025825781</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.04846407339621</c:v>
+                  <c:v>10.80380278531956</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.24410812793835</c:v>
+                  <c:v>16.040911929842</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>7.649768807982493</c:v>
@@ -12566,7 +12566,7 @@
         <v>10.78849792480469</v>
       </c>
       <c r="L2">
-        <v>10.80988597869873</v>
+        <v>10.89763832092285</v>
       </c>
       <c r="M2">
         <v>10.82431983947754</v>
@@ -12622,7 +12622,7 @@
         <v>11.09786701202393</v>
       </c>
       <c r="L3">
-        <v>11.08655166625977</v>
+        <v>11.17911243438721</v>
       </c>
       <c r="M3">
         <v>11.10275936126709</v>
@@ -12678,7 +12678,7 @@
         <v>11.31296348571777</v>
       </c>
       <c r="L4">
-        <v>11.33691310882568</v>
+        <v>11.4369945526123</v>
       </c>
       <c r="M4">
         <v>11.32342147827148</v>
@@ -12734,7 +12734,7 @@
         <v>11.36948013305664</v>
       </c>
       <c r="L5">
-        <v>11.57836532592773</v>
+        <v>11.68558597564697</v>
       </c>
       <c r="M5">
         <v>11.44236660003662</v>
@@ -12790,7 +12790,7 @@
         <v>12.26796245574951</v>
       </c>
       <c r="L6">
-        <v>12.3137035369873</v>
+        <v>12.70683670043945</v>
       </c>
       <c r="M6">
         <v>12.4367504119873</v>
@@ -12846,7 +12846,7 @@
         <v>12.05098724365234</v>
       </c>
       <c r="L7">
-        <v>12.26032733917236</v>
+        <v>12.33250141143799</v>
       </c>
       <c r="M7">
         <v>12.07330703735352</v>
@@ -12902,7 +12902,7 @@
         <v>12.41473579406738</v>
       </c>
       <c r="L8">
-        <v>12.41421699523926</v>
+        <v>12.50737571716309</v>
       </c>
       <c r="M8">
         <v>12.30055809020996</v>
@@ -12958,7 +12958,7 @@
         <v>11.824538230896</v>
       </c>
       <c r="L9">
-        <v>12.60287666320801</v>
+        <v>12.69899463653564</v>
       </c>
       <c r="M9">
         <v>11.93213081359863</v>
@@ -13014,7 +13014,7 @@
         <v>11.75459957122803</v>
       </c>
       <c r="L10">
-        <v>12.79858112335205</v>
+        <v>12.8897762298584</v>
       </c>
       <c r="M10">
         <v>11.88990116119385</v>
@@ -13070,7 +13070,7 @@
         <v>11.74276924133301</v>
       </c>
       <c r="L11">
-        <v>13.01634979248047</v>
+        <v>13.10569000244141</v>
       </c>
       <c r="M11">
         <v>11.92905712127686</v>
@@ -13126,7 +13126,7 @@
         <v>11.72309684753418</v>
       </c>
       <c r="L12">
-        <v>13.4949893951416</v>
+        <v>13.70723533630371</v>
       </c>
       <c r="M12">
         <v>12.01075172424316</v>
@@ -14089,7 +14089,7 @@
         <v>0.003783548494662448</v>
       </c>
       <c r="L2">
-        <v>0.2020397216015546</v>
+        <v>1.015458447620654</v>
       </c>
       <c r="M2">
         <v>0.3358341292339917</v>
@@ -14145,7 +14145,7 @@
         <v>0.003944485703510914</v>
       </c>
       <c r="L3">
-        <v>-0.09801918068477189</v>
+        <v>0.7360547821174457</v>
       </c>
       <c r="M3">
         <v>0.04802991415457925</v>
@@ -14201,7 +14201,7 @@
         <v>0.004299446501065951</v>
       </c>
       <c r="L4">
-        <v>0.216009250385607</v>
+        <v>1.100708885994872</v>
       </c>
       <c r="M4">
         <v>0.09674597656110784</v>
@@ -14257,7 +14257,7 @@
         <v>0.00473106734222295</v>
       </c>
       <c r="L5">
-        <v>1.84206287957589</v>
+        <v>2.785164245210203</v>
       </c>
       <c r="M5">
         <v>0.6458326342985599</v>
@@ -14313,7 +14313,7 @@
         <v>-0.2972274581778067</v>
       </c>
       <c r="L6">
-        <v>0.07451419288433403</v>
+        <v>3.26954079291657</v>
       </c>
       <c r="M6">
         <v>1.074526593831759</v>
@@ -14369,7 +14369,7 @@
         <v>-0.75289990282148</v>
       </c>
       <c r="L7">
-        <v>0.97114120637245</v>
+        <v>1.565537933357675</v>
       </c>
       <c r="M7">
         <v>-0.5690830291644744</v>
@@ -14425,7 +14425,7 @@
         <v>-0.6853718025302769</v>
       </c>
       <c r="L8">
-        <v>-0.6895220570003913</v>
+        <v>0.05572326957656859</v>
       </c>
       <c r="M8">
         <v>-1.598763468300524</v>
@@ -14481,7 +14481,7 @@
         <v>-0.7017867857237792</v>
       </c>
       <c r="L9">
-        <v>5.834419034359839</v>
+        <v>6.641583155515418</v>
       </c>
       <c r="M9">
         <v>0.201736972148292</v>
@@ -14537,7 +14537,7 @@
         <v>-0.7440257613474111</v>
       </c>
       <c r="L10">
-        <v>8.071366495559996</v>
+        <v>8.841419025825781</v>
       </c>
       <c r="M10">
         <v>0.3984624235302547</v>
@@ -14593,7 +14593,7 @@
         <v>-0.7191924326155674</v>
       </c>
       <c r="L11">
-        <v>10.04846407339621</v>
+        <v>10.80380278531956</v>
       </c>
       <c r="M11">
         <v>0.8558032758704481</v>
@@ -14649,7 +14649,7 @@
         <v>-0.7561469943685784</v>
       </c>
       <c r="L12">
-        <v>14.24410812793835</v>
+        <v>16.040911929842</v>
       </c>
       <c r="M12">
         <v>1.679043866181562</v>

--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="36">
   <si>
     <t>SC  ·  W-M L-M  ·  Netback</t>
   </si>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Net</t>
   </si>
   <si>
     <t>Terms are the dispatch objective's own, signed as they enter it, so they sum to total_cost exactly. lng_revenue is negative: the system is PAID for an export cargo, which is why a total across components is below the sum of the costs.</t>
@@ -1292,6 +1295,165 @@
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'system cost'!$J$86</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1A1D21"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'system cost'!$A$87:$A$103</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>SC  ·  W-M L-M  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Acc  ·  W-M L-M  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SG  ·  W-M L-M  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SC  ·  W-M L-L  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SC  ·  W-M L-H  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>SC  ·  W-L L-M  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>SC  ·  W-H L-M  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>SC  ·  W-M L-M  ·  Dunk27  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>SC  ·  W-M L-M  ·  No imports  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SC  ·  W-M L-M  ·  GSOO exp  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SC  ·  W-M L-M  ·  DC series NSW  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>SC  ·  W-H L-M  ·  DC series NSW  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>SC  ·  W-M L-M  ·  DC series NSW  ·  No imports  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>SC  ·  W-M L-M  ·  Res20% breaks contracts  ·  DC series NSW  ·  Netback</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>SC  ·  W-M L-M  ·  Res20% uncontracted only  ·  DC series NSW  ·  Netback</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'system cost'!$J$87:$J$103</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>154.1124537275826</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>176.0373871084164</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>162.4829105272608</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>138.3313022961085</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>171.6319968506561</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>152.2076164902062</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167.453961968025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>154.1976166599476</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>154.1124537275826</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>164.8775272642109</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>122.5491113134043</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>162.379071020579</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>174.9131083718059</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>162.8822683919494</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94.1884337670903</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>101.7474562056919</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>130.8866081460092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="50010001"/>
         <c:scaling>
@@ -16396,7 +16558,7 @@
         <v>25</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -16945,12 +17107,12 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/domestic_price_summary.xlsx
+++ b/output/domestic_price_summary.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="38">
   <si>
     <t>SC  ·  W-M L-M  ·  Netback</t>
   </si>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t>NOT comparable across reservation levels: the reserved tranche is priced at $0 in dispatch, so reserving more always lowers the figure -- totals included. See docs/scenarios.md.</t>
+  </si>
+  <si>
+    <t>lng_revenue IS SPOT ONLY. Foundation cargoes -- the contracted, must-serve volume, around 93% of exports -- are served as demand and earn nothing in the objective, while the system still pays to produce and ship them. So the Net is the net of the MODEL'S OBJECTIVE, not the net cash position: it overstates net system cost by the unpriced foundation revenue. That is harmless for the build and dispatch decisions, which a constant cannot move, but it is NOT constant across scenarios -- planned export volume differs between them -- so read the Net dots against each other with care.</t>
+  </si>
+  <si>
+    <t>Worked example, 2035 central: 1,180 PJ foundation and 109 PJ spot were exported; lng_revenue books 109 PJ x $8.02/GJ = $0.88bn and nothing for the other 1,180 PJ. At LNG Low the $5.92 netback clears no spot cargo at all, so the term is $0.00bn and the bar sits on the axis -- which is why LNG Low looks like the scenario with the least export revenue.</t>
   </si>
 </sst>
 </file>
@@ -13547,7 +13553,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -17113,6 +17119,16 @@
     <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
